--- a/results/Int Task Remove ACC -0.7/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_7_permute.xlsx
@@ -440,77 +440,77 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6487227343495877</v>
+        <v>0.6713066037586886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6456920114447045</v>
+        <v>0.6951720416354812</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6362167340906292</v>
+        <v>0.6929947766166751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.626344729088308</v>
+        <v>0.6929947766166751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6288164805007375</v>
+        <v>0.6918618329843709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6469994362914611</v>
+        <v>0.6832700148111656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6815030964494257</v>
+        <v>0.6824601772287016</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6717797162824922</v>
+        <v>0.6765173549595298</v>
       </c>
     </row>
     <row r="10">
@@ -520,737 +520,737 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6704150521233021</v>
+        <v>0.6658860408712376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6658710402238412</v>
+        <v>0.6438530505000741</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6682391687430721</v>
+        <v>0.643558564106451</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.689058883067585</v>
+        <v>0.6534578071264128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.677980312834554</v>
+        <v>0.6527829753705159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.677980312834554</v>
+        <v>0.6126392691684589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6895592336090295</v>
+        <v>0.6118580512422115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.68982371870786</v>
+        <v>0.6160503374356157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.68982371870786</v>
+        <v>0.6155813698275399</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6961824141884019</v>
+        <v>0.6155813698275399</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6975362226159234</v>
+        <v>0.6170524201570805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6560167991460684</v>
+        <v>0.5842217269376889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6621518665542407</v>
+        <v>0.5983460207229996</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6791446394002267</v>
+        <v>0.5865653807164309</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.657536996333526</v>
+        <v>0.5580278333064901</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6352748513356892</v>
+        <v>0.5568648883793932</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6365836578210218</v>
+        <v>0.5613230413102039</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6283735666486658</v>
+        <v>0.5511593131914114</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6250483573501593</v>
+        <v>0.5410392053762321</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6210796992291246</v>
+        <v>0.5005710114857589</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.594925280985811</v>
+        <v>0.5054545117210322</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6065886790903607</v>
+        <v>0.4993780652638693</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5854405295386432</v>
+        <v>0.508144364651527</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5699624273258109</v>
+        <v>0.4893112492223348</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4899817386855643</v>
+        <v>0.5079754099913786</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4982749255494184</v>
+        <v>0.4999561823194475</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4941534976772681</v>
+        <v>0.4995008337201922</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5353225770796424</v>
+        <v>0.4810247731744212</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5746305893201706</v>
+        <v>0.4809511515760154</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5062736260196492</v>
+        <v>0.4802176988691091</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5062736260196492</v>
+        <v>0.4802176988691091</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4832876997849381</v>
+        <v>0.4862396692909904</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5035837730891544</v>
+        <v>0.46657066252333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.491609506305009</v>
+        <v>0.4629959687733892</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4823728576706995</v>
+        <v>0.493230957862392</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.481989749031274</v>
+        <v>0.5087799183964782</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4929510773622862</v>
+        <v>0.5084268110518454</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4993139177585559</v>
+        <v>0.51497360675566</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5102466264333513</v>
+        <v>0.51497360675566</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4911146823178685</v>
+        <v>0.5111780482105017</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4949552428052158</v>
+        <v>0.5166805225278144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4931310851310425</v>
+        <v>0.5120028864403622</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5489903380040612</v>
+        <v>0.5120028864403622</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5306179003514888</v>
+        <v>0.5120028864403622</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5274263152409735</v>
+        <v>0.511428914300512</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5305306597442627</v>
+        <v>0.5096483769299517</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5486358490208525</v>
+        <v>0.507323868714334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5486358490208525</v>
+        <v>0.5050866011059425</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5624056538229545</v>
+        <v>0.5110458056610864</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5624056538229545</v>
+        <v>0.5104718335212362</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5072731428409015</v>
+        <v>0.5110021853574733</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.621310235494374</v>
+        <v>0.5103695922666136</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5646565404401663</v>
+        <v>0.5061923067206058</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6084307980660217</v>
+        <v>0.5064717924668327</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5808159878478966</v>
+        <v>0.5039564207507903</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.586573275794008</v>
+        <v>0.5003517257060568</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5818956397065558</v>
+        <v>0.5008520762475013</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6058919384941877</v>
+        <v>0.5007198336980859</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6400355831146396</v>
+        <v>0.5007198336980859</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6270400880459052</v>
+        <v>0.5043531483990361</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6061631344089586</v>
+        <v>0.504147284251215</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6061631344089586</v>
+        <v>0.5042945274480267</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5451290529380741</v>
+        <v>0.504264526153234</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.569635176360243</v>
+        <v>0.5022195036838432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.566132722570132</v>
+        <v>0.5060886838274072</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5734129709808529</v>
+        <v>0.5130908281304772</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5707803573627914</v>
+        <v>0.5082223285426003</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5905585135779544</v>
+        <v>0.5085754358872331</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5887193552563847</v>
+        <v>0.5048098786368674</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5405838567769767</v>
+        <v>0.5048098786368674</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4634059206765765</v>
+        <v>0.5037505566029692</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4751634675812325</v>
+        <v>0.5031179635121095</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4652873176631834</v>
+        <v>0.5025589920196556</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4552422130849857</v>
+        <v>0.5028234771184862</v>
       </c>
     </row>
     <row r="84">
@@ -1260,67 +1260,67 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4637304083649926</v>
+        <v>0.5049857414898959</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4637304083649926</v>
+        <v>0.5091044060848942</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4915877948416721</v>
+        <v>0.5031329641595058</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4927493581301929</v>
+        <v>0.5024853704212497</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4927493581301929</v>
+        <v>0.5032652067089212</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4809345719131036</v>
+        <v>0.50185277733039</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.489694160484821</v>
+        <v>0.500602591796067</v>
       </c>
     </row>
   </sheetData>
